--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/50.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/50.xlsx
@@ -426,13 +426,13 @@
         <v>-1.318810158705459</v>
       </c>
       <c r="E2">
-        <v>-6.008372333136617</v>
+        <v>-6.721837941519089</v>
       </c>
       <c r="F2">
-        <v>-8.165244284924992</v>
+        <v>-8.795708503552421</v>
       </c>
       <c r="G2">
-        <v>-6.142549560963519</v>
+        <v>-6.236274415725825</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-0.2818183128550042</v>
       </c>
       <c r="E3">
-        <v>-6.420884615917333</v>
+        <v>-7.38813043616366</v>
       </c>
       <c r="F3">
-        <v>-8.136521798516103</v>
+        <v>-8.54548613632482</v>
       </c>
       <c r="G3">
-        <v>-5.596478384806276</v>
+        <v>-6.007399849868312</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>0.6028016662960171</v>
       </c>
       <c r="E4">
-        <v>-7.486697201414612</v>
+        <v>-8.336669130284301</v>
       </c>
       <c r="F4">
-        <v>-8.15535126999772</v>
+        <v>-8.219719017298361</v>
       </c>
       <c r="G4">
-        <v>-5.676060589024815</v>
+        <v>-6.416371403607717</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>1.160350101801776</v>
       </c>
       <c r="E5">
-        <v>-7.961462416378773</v>
+        <v>-6.915557002619212</v>
       </c>
       <c r="F5">
-        <v>-7.981215677918533</v>
+        <v>-8.486597615565119</v>
       </c>
       <c r="G5">
-        <v>-6.018582872699969</v>
+        <v>-6.609316618727521</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>1.415266142743451</v>
       </c>
       <c r="E6">
-        <v>-8.289550358234491</v>
+        <v>-8.851579267326459</v>
       </c>
       <c r="F6">
-        <v>-7.74395713138824</v>
+        <v>-8.217269420173656</v>
       </c>
       <c r="G6">
-        <v>-6.046143164314403</v>
+        <v>-6.458577548687885</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>1.367070799552835</v>
       </c>
       <c r="E7">
-        <v>-8.688549674576318</v>
+        <v>-7.522499316919254</v>
       </c>
       <c r="F7">
-        <v>-8.04990496273593</v>
+        <v>-7.784051022196462</v>
       </c>
       <c r="G7">
-        <v>-5.924758701571485</v>
+        <v>-7.574108905237322</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>1.066694626497255</v>
       </c>
       <c r="E8">
-        <v>-9.987728111110874</v>
+        <v>-9.662076488271284</v>
       </c>
       <c r="F8">
-        <v>-7.887904517233799</v>
+        <v>-8.108999365264639</v>
       </c>
       <c r="G8">
-        <v>-7.269955844362322</v>
+        <v>-8.057471727789691</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>0.5726881276827898</v>
       </c>
       <c r="E9">
-        <v>-10.57396624224785</v>
+        <v>-10.25744402300772</v>
       </c>
       <c r="F9">
-        <v>-7.55707468632216</v>
+        <v>-8.121591410998297</v>
       </c>
       <c r="G9">
-        <v>-7.155026945420983</v>
+        <v>-7.67187262555754</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.02996434221330772</v>
       </c>
       <c r="E10">
-        <v>-10.87830686640734</v>
+        <v>-10.78828533160886</v>
       </c>
       <c r="F10">
-        <v>-7.276717562935576</v>
+        <v>-7.683721272820979</v>
       </c>
       <c r="G10">
-        <v>-7.841326209530675</v>
+        <v>-7.398845313842767</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.6639075549814019</v>
       </c>
       <c r="E11">
-        <v>-11.16519475174128</v>
+        <v>-11.18031532645289</v>
       </c>
       <c r="F11">
-        <v>-7.124005948553975</v>
+        <v>-7.776051723617578</v>
       </c>
       <c r="G11">
-        <v>-7.958248056886655</v>
+        <v>-8.153517274975027</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.252036340680413</v>
       </c>
       <c r="E12">
-        <v>-11.20740012949276</v>
+        <v>-11.98238052879543</v>
       </c>
       <c r="F12">
-        <v>-7.220202225490161</v>
+        <v>-7.623319916985555</v>
       </c>
       <c r="G12">
-        <v>-7.883055636053188</v>
+        <v>-9.15382178348459</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.735623695629818</v>
       </c>
       <c r="E13">
-        <v>-11.99261940852677</v>
+        <v>-12.11771850298867</v>
       </c>
       <c r="F13">
-        <v>-6.883449334454779</v>
+        <v>-7.390832284525523</v>
       </c>
       <c r="G13">
-        <v>-8.517409130106175</v>
+        <v>-9.469376363196842</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.077905658288437</v>
       </c>
       <c r="E14">
-        <v>-12.00268620624582</v>
+        <v>-12.71128370507005</v>
       </c>
       <c r="F14">
-        <v>-6.640023837089765</v>
+        <v>-7.151109491590806</v>
       </c>
       <c r="G14">
-        <v>-7.909093076719556</v>
+        <v>-9.189075782932289</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.26531207631308</v>
       </c>
       <c r="E15">
-        <v>-13.40699769534245</v>
+        <v>-13.07470280113361</v>
       </c>
       <c r="F15">
-        <v>-6.618260946326274</v>
+        <v>-6.948880540277639</v>
       </c>
       <c r="G15">
-        <v>-7.97380431037569</v>
+        <v>-8.088633892950851</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.309658222800576</v>
       </c>
       <c r="E16">
-        <v>-13.390197056774</v>
+        <v>-12.81460536802906</v>
       </c>
       <c r="F16">
-        <v>-6.293487602761755</v>
+        <v>-7.000482826046881</v>
       </c>
       <c r="G16">
-        <v>-7.765683554503868</v>
+        <v>-7.637913049415696</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.240650773174913</v>
       </c>
       <c r="E17">
-        <v>-13.46229036297611</v>
+        <v>-14.39812215903123</v>
       </c>
       <c r="F17">
-        <v>-5.734430308302617</v>
+        <v>-6.487837617145611</v>
       </c>
       <c r="G17">
-        <v>-7.667820517817472</v>
+        <v>-7.403380761231568</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.099178721845332</v>
       </c>
       <c r="E18">
-        <v>-14.17278982088356</v>
+        <v>-16.51727138413466</v>
       </c>
       <c r="F18">
-        <v>-5.684354319109379</v>
+        <v>-6.455462313042761</v>
       </c>
       <c r="G18">
-        <v>-7.520650215869171</v>
+        <v>-7.956635821209029</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.933511264531769</v>
       </c>
       <c r="E19">
-        <v>-15.69185736980856</v>
+        <v>-15.45958288100714</v>
       </c>
       <c r="F19">
-        <v>-5.044033510790732</v>
+        <v>-5.660078482984566</v>
       </c>
       <c r="G19">
-        <v>-7.291381695092484</v>
+        <v>-6.469664565698904</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.788083135713048</v>
       </c>
       <c r="E20">
-        <v>-16.17042650293917</v>
+        <v>-16.79715372017872</v>
       </c>
       <c r="F20">
-        <v>-4.663857779112874</v>
+        <v>-5.391687841495042</v>
       </c>
       <c r="G20">
-        <v>-6.792293781228578</v>
+        <v>-7.016298534597824</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.697988216191388</v>
       </c>
       <c r="E21">
-        <v>-17.01857345678376</v>
+        <v>-17.58114125428265</v>
       </c>
       <c r="F21">
-        <v>-4.377153954270167</v>
+        <v>-5.136349312307614</v>
       </c>
       <c r="G21">
-        <v>-6.494308266693239</v>
+        <v>-6.803635710246121</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.689153150968839</v>
       </c>
       <c r="E22">
-        <v>-17.56337605075056</v>
+        <v>-17.5864259834496</v>
       </c>
       <c r="F22">
-        <v>-4.063501789570341</v>
+        <v>-4.751913411717222</v>
       </c>
       <c r="G22">
-        <v>-6.732366285876691</v>
+        <v>-6.74654535242139</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.771629470337358</v>
       </c>
       <c r="E23">
-        <v>-18.71970830318716</v>
+        <v>-19.44645139736012</v>
       </c>
       <c r="F23">
-        <v>-3.911717039075752</v>
+        <v>-4.373064033743544</v>
       </c>
       <c r="G23">
-        <v>-6.036466439703113</v>
+        <v>-5.789751343934467</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.94046494323539</v>
       </c>
       <c r="E24">
-        <v>-17.77985975068724</v>
+        <v>-18.58332425149815</v>
       </c>
       <c r="F24">
-        <v>-3.46444443887847</v>
+        <v>-4.482650148268292</v>
       </c>
       <c r="G24">
-        <v>-6.235853976442338</v>
+        <v>-6.621876828503515</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.180953732609196</v>
       </c>
       <c r="E25">
-        <v>-19.83049316405461</v>
+        <v>-19.54750882331529</v>
       </c>
       <c r="F25">
-        <v>-3.399297112340953</v>
+        <v>-4.046229101003601</v>
       </c>
       <c r="G25">
-        <v>-6.941225293403771</v>
+        <v>-6.698880117746963</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.466151771522658</v>
       </c>
       <c r="E26">
-        <v>-18.76624290208998</v>
+        <v>-20.05062228556747</v>
       </c>
       <c r="F26">
-        <v>-3.421112661326131</v>
+        <v>-4.016335068143766</v>
       </c>
       <c r="G26">
-        <v>-7.578409303892836</v>
+        <v>-6.871342987615296</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.760986111896085</v>
       </c>
       <c r="E27">
-        <v>-19.12017484510747</v>
+        <v>-19.58291696158127</v>
       </c>
       <c r="F27">
-        <v>-3.808936108869647</v>
+        <v>-4.235702884873819</v>
       </c>
       <c r="G27">
-        <v>-7.112016337774771</v>
+        <v>-7.092427839818904</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.029968223032845</v>
       </c>
       <c r="E28">
-        <v>-19.20502486258919</v>
+        <v>-19.52764240784364</v>
       </c>
       <c r="F28">
-        <v>-3.505989796158193</v>
+        <v>-4.546004719709532</v>
       </c>
       <c r="G28">
-        <v>-7.777042036249107</v>
+        <v>-7.18606662039719</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.237549039327256</v>
       </c>
       <c r="E29">
-        <v>-18.66192497484928</v>
+        <v>-18.03034323347351</v>
       </c>
       <c r="F29">
-        <v>-3.638538854603855</v>
+        <v>-4.088263823411195</v>
       </c>
       <c r="G29">
-        <v>-7.432328171426955</v>
+        <v>-8.014878248881427</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.352141810974373</v>
       </c>
       <c r="E30">
-        <v>-18.74657573947466</v>
+        <v>-18.27136673405775</v>
       </c>
       <c r="F30">
-        <v>-3.092496059431319</v>
+        <v>-4.102451452854659</v>
       </c>
       <c r="G30">
-        <v>-7.407846687164045</v>
+        <v>-7.50562033912088</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.350895901474403</v>
       </c>
       <c r="E31">
-        <v>-18.48098526739881</v>
+        <v>-19.72057351446643</v>
       </c>
       <c r="F31">
-        <v>-3.488201611315977</v>
+        <v>-4.438234324016835</v>
       </c>
       <c r="G31">
-        <v>-7.966832301469985</v>
+        <v>-7.905613693357782</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.220230435583895</v>
       </c>
       <c r="E32">
-        <v>-18.49428992403334</v>
+        <v>-17.78258589203985</v>
       </c>
       <c r="F32">
-        <v>-3.525271415678668</v>
+        <v>-4.156322793274247</v>
       </c>
       <c r="G32">
-        <v>-7.36085680377963</v>
+        <v>-7.186175868399985</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.955474202707304</v>
       </c>
       <c r="E33">
-        <v>-18.11649292299543</v>
+        <v>-17.75472219147066</v>
       </c>
       <c r="F33">
-        <v>-3.41306347601091</v>
+        <v>-4.497862435439045</v>
       </c>
       <c r="G33">
-        <v>-7.90948372109319</v>
+        <v>-7.125437289390977</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.563071379819194</v>
       </c>
       <c r="E34">
-        <v>-18.82017249904732</v>
+        <v>-18.39116298545666</v>
       </c>
       <c r="F34">
-        <v>-3.719752085800548</v>
+        <v>-4.167069029763462</v>
       </c>
       <c r="G34">
-        <v>-6.794495294012194</v>
+        <v>-7.452740995222102</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.058790450441786</v>
       </c>
       <c r="E35">
-        <v>-17.82028543815371</v>
+        <v>-17.87279762274665</v>
       </c>
       <c r="F35">
-        <v>-3.632824843660949</v>
+        <v>-4.747966816575947</v>
       </c>
       <c r="G35">
-        <v>-6.587043268339304</v>
+        <v>-7.78643074339848</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.46154511098329</v>
       </c>
       <c r="E36">
-        <v>-17.03061466917016</v>
+        <v>-18.15815488386599</v>
       </c>
       <c r="F36">
-        <v>-4.015725341366322</v>
+        <v>-4.786456413291829</v>
       </c>
       <c r="G36">
-        <v>-7.144393473148844</v>
+        <v>-7.111817705042415</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.7975274446351269</v>
       </c>
       <c r="E37">
-        <v>-17.89371011571408</v>
+        <v>-16.99959462221762</v>
       </c>
       <c r="F37">
-        <v>-3.953251310414067</v>
+        <v>-5.014565494822151</v>
       </c>
       <c r="G37">
-        <v>-6.40690986445648</v>
+        <v>-6.654267206059744</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.09437176426038697</v>
       </c>
       <c r="E38">
-        <v>-17.32378807642674</v>
+        <v>-16.15727128594688</v>
       </c>
       <c r="F38">
-        <v>-3.78799159813796</v>
+        <v>-4.95582980168329</v>
       </c>
       <c r="G38">
-        <v>-6.436112186658391</v>
+        <v>-7.177710803456069</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.6228767106111566</v>
       </c>
       <c r="E39">
-        <v>-16.77183502200184</v>
+        <v>-17.54047102921976</v>
       </c>
       <c r="F39">
-        <v>-3.762967460968102</v>
+        <v>-4.955337269143588</v>
       </c>
       <c r="G39">
-        <v>-6.278182611707459</v>
+        <v>-5.187569731432117</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.327619802110815</v>
       </c>
       <c r="E40">
-        <v>-16.14903399172693</v>
+        <v>-16.18889361994245</v>
       </c>
       <c r="F40">
-        <v>-4.084102636118378</v>
+        <v>-4.428855617585603</v>
       </c>
       <c r="G40">
-        <v>-6.2176757708862</v>
+        <v>-4.607611811134894</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.000399353188024</v>
       </c>
       <c r="E41">
-        <v>-16.55094058838169</v>
+        <v>-17.33255067363158</v>
       </c>
       <c r="F41">
-        <v>-3.837788855090081</v>
+        <v>-4.696467867617687</v>
       </c>
       <c r="G41">
-        <v>-6.074041131573841</v>
+        <v>-5.617291784611673</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>2.624791608192681</v>
       </c>
       <c r="E42">
-        <v>-15.76360651198609</v>
+        <v>-16.10965891023024</v>
       </c>
       <c r="F42">
-        <v>-3.906219203990303</v>
+        <v>-5.103002800552121</v>
       </c>
       <c r="G42">
-        <v>-6.079549879351188</v>
+        <v>-4.460994370291651</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>3.185784044153285</v>
       </c>
       <c r="E43">
-        <v>-15.92518246457977</v>
+        <v>-16.0422752169961</v>
       </c>
       <c r="F43">
-        <v>-4.108168631209396</v>
+        <v>-4.795278447093785</v>
       </c>
       <c r="G43">
-        <v>-5.301081716882647</v>
+        <v>-5.197080928766442</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>3.676174818756574</v>
       </c>
       <c r="E44">
-        <v>-14.73358245657143</v>
+        <v>-15.17143155142506</v>
       </c>
       <c r="F44">
-        <v>-4.032842034900392</v>
+        <v>-4.9492352502514</v>
       </c>
       <c r="G44">
-        <v>-5.541718651041191</v>
+        <v>-4.039134862767863</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>4.090278583764519</v>
       </c>
       <c r="E45">
-        <v>-15.39888321540832</v>
+        <v>-15.24577550920899</v>
       </c>
       <c r="F45">
-        <v>-4.195939196748966</v>
+        <v>-5.061345000152401</v>
       </c>
       <c r="G45">
-        <v>-4.60095099350988</v>
+        <v>-4.283373670473134</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.425573293957574</v>
       </c>
       <c r="E46">
-        <v>-14.06270261775709</v>
+        <v>-15.6028502131878</v>
       </c>
       <c r="F46">
-        <v>-4.210961439209866</v>
+        <v>-5.012819459050379</v>
       </c>
       <c r="G46">
-        <v>-4.216580103672799</v>
+        <v>-4.58473594145853</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>4.685846234398451</v>
       </c>
       <c r="E47">
-        <v>-13.55531427604167</v>
+        <v>-14.7482637693043</v>
       </c>
       <c r="F47">
-        <v>-4.37896175457264</v>
+        <v>-5.181530858369185</v>
       </c>
       <c r="G47">
-        <v>-5.111807896765895</v>
+        <v>-3.777217741882884</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>4.874321723060476</v>
       </c>
       <c r="E48">
-        <v>-13.78537886952736</v>
+        <v>-14.04291318634357</v>
       </c>
       <c r="F48">
-        <v>-4.458736980798114</v>
+        <v>-5.092108487559813</v>
       </c>
       <c r="G48">
-        <v>-4.146773940431727</v>
+        <v>-4.687101320078334</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>4.993866830995662</v>
       </c>
       <c r="E49">
-        <v>-13.06796896028421</v>
+        <v>-13.33026723175649</v>
       </c>
       <c r="F49">
-        <v>-4.694224548188467</v>
+        <v>-5.491462106020685</v>
       </c>
       <c r="G49">
-        <v>-4.026140971526224</v>
+        <v>-4.22165848053004</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>5.049130503162123</v>
       </c>
       <c r="E50">
-        <v>-12.80031350406085</v>
+        <v>-12.98263439608366</v>
       </c>
       <c r="F50">
-        <v>-4.597225728279632</v>
+        <v>-5.297196028050347</v>
       </c>
       <c r="G50">
-        <v>-3.642001819876891</v>
+        <v>-4.093278835062644</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>5.042189582324832</v>
       </c>
       <c r="E51">
-        <v>-12.50876129049902</v>
+        <v>-13.66546487780425</v>
       </c>
       <c r="F51">
-        <v>-4.603281819700272</v>
+        <v>-5.390769292064087</v>
       </c>
       <c r="G51">
-        <v>-3.375900169430273</v>
+        <v>-3.537017799735524</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>4.973495565852419</v>
       </c>
       <c r="E52">
-        <v>-12.72187580577399</v>
+        <v>-12.72108785129666</v>
       </c>
       <c r="F52">
-        <v>-5.010245145084832</v>
+        <v>-5.362634756476305</v>
       </c>
       <c r="G52">
-        <v>-3.604960125837986</v>
+        <v>-3.57073901659854</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>4.846324940935606</v>
       </c>
       <c r="E53">
-        <v>-12.86132563436619</v>
+        <v>-13.82342710813981</v>
       </c>
       <c r="F53">
-        <v>-4.996433645796285</v>
+        <v>-5.480116436842477</v>
       </c>
       <c r="G53">
-        <v>-3.623820303775214</v>
+        <v>-2.775625431158543</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>4.664858614148107</v>
       </c>
       <c r="E54">
-        <v>-12.40243272079892</v>
+        <v>-11.84039022628492</v>
       </c>
       <c r="F54">
-        <v>-5.2079454893328</v>
+        <v>-5.341367961590826</v>
       </c>
       <c r="G54">
-        <v>-3.596120969248132</v>
+        <v>-3.468860288173008</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>4.431698437881525</v>
       </c>
       <c r="E55">
-        <v>-11.12934735149656</v>
+        <v>-12.81945083521726</v>
       </c>
       <c r="F55">
-        <v>-5.073653562527197</v>
+        <v>-5.944583332163685</v>
       </c>
       <c r="G55">
-        <v>-2.986007289633688</v>
+        <v>-3.126437320864032</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>4.152246111120033</v>
       </c>
       <c r="E56">
-        <v>-11.64101057267522</v>
+        <v>-10.21928257254508</v>
       </c>
       <c r="F56">
-        <v>-5.081456481572567</v>
+        <v>-5.574997050089411</v>
       </c>
       <c r="G56">
-        <v>-2.874885518062511</v>
+        <v>-3.026468777214661</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>3.831259962003526</v>
       </c>
       <c r="E57">
-        <v>-11.7006913316223</v>
+        <v>-10.39612853949263</v>
       </c>
       <c r="F57">
-        <v>-4.999597890215332</v>
+        <v>-5.784591817615288</v>
       </c>
       <c r="G57">
-        <v>-3.990890282624064</v>
+        <v>-3.395594604843398</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>3.472461994505294</v>
       </c>
       <c r="E58">
-        <v>-10.96379992719815</v>
+        <v>-11.43306304624299</v>
       </c>
       <c r="F58">
-        <v>-5.286271624645646</v>
+        <v>-5.671062275361096</v>
       </c>
       <c r="G58">
-        <v>-3.620781222970163</v>
+        <v>-3.623965967778942</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>3.085757558340249</v>
       </c>
       <c r="E59">
-        <v>-10.99897258481573</v>
+        <v>-10.38847088994565</v>
       </c>
       <c r="F59">
-        <v>-4.839425041339617</v>
+        <v>-6.077141100991882</v>
       </c>
       <c r="G59">
-        <v>-3.08461188852088</v>
+        <v>-3.555550233664364</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>2.680792108266523</v>
       </c>
       <c r="E60">
-        <v>-11.28896700331892</v>
+        <v>-10.88913897623369</v>
       </c>
       <c r="F60">
-        <v>-5.296055759791231</v>
+        <v>-5.82067497319266</v>
       </c>
       <c r="G60">
-        <v>-4.272962004752126</v>
+        <v>-4.450678710391282</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>2.267989283120923</v>
       </c>
       <c r="E61">
-        <v>-11.06016132560737</v>
+        <v>-10.35942978613446</v>
       </c>
       <c r="F61">
-        <v>-5.362298218969275</v>
+        <v>-6.28171710447173</v>
       </c>
       <c r="G61">
-        <v>-3.758195347214232</v>
+        <v>-3.886449191951137</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.862657178072054</v>
       </c>
       <c r="E62">
-        <v>-10.83107941098135</v>
+        <v>-9.623371620927726</v>
       </c>
       <c r="F62">
-        <v>-5.36428972915794</v>
+        <v>-6.0077660715131</v>
       </c>
       <c r="G62">
-        <v>-3.950306304858139</v>
+        <v>-4.496685361750534</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>1.478488165211387</v>
       </c>
       <c r="E63">
-        <v>-10.68865437496611</v>
+        <v>-9.598333688139316</v>
       </c>
       <c r="F63">
-        <v>-5.604724001975168</v>
+        <v>-5.999467452516196</v>
       </c>
       <c r="G63">
-        <v>-3.312801171451765</v>
+        <v>-4.663503751474409</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>1.132273665418171</v>
       </c>
       <c r="E64">
-        <v>-9.505866777376696</v>
+        <v>-10.02709866413356</v>
       </c>
       <c r="F64">
-        <v>-5.651792533634986</v>
+        <v>-6.362974679434055</v>
       </c>
       <c r="G64">
-        <v>-4.056525158485655</v>
+        <v>-4.466036331147961</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.8423074757571072</v>
       </c>
       <c r="E65">
-        <v>-10.38963017929162</v>
+        <v>-11.33541103274159</v>
       </c>
       <c r="F65">
-        <v>-5.527244357474124</v>
+        <v>-6.075443368250531</v>
       </c>
       <c r="G65">
-        <v>-4.58341503378836</v>
+        <v>-3.508603387371959</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.6207702939342261</v>
       </c>
       <c r="E66">
-        <v>-9.997056767566676</v>
+        <v>-10.76042163103967</v>
       </c>
       <c r="F66">
-        <v>-5.746986720653178</v>
+        <v>-6.061146463098901</v>
       </c>
       <c r="G66">
-        <v>-3.585550397341239</v>
+        <v>-5.05300598689736</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.4793425265410119</v>
       </c>
       <c r="E67">
-        <v>-10.62895097364898</v>
+        <v>-10.64010460512987</v>
       </c>
       <c r="F67">
-        <v>-5.526846847289349</v>
+        <v>-6.400980453992771</v>
       </c>
       <c r="G67">
-        <v>-4.323484240226944</v>
+        <v>-4.576628415432855</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.4234305011911931</v>
       </c>
       <c r="E68">
-        <v>-10.3838337325618</v>
+        <v>-10.62976609897036</v>
       </c>
       <c r="F68">
-        <v>-5.821275197734612</v>
+        <v>-6.811829401840861</v>
       </c>
       <c r="G68">
-        <v>-4.33172087752865</v>
+        <v>-4.944469751392354</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.4506276806591454</v>
       </c>
       <c r="E69">
-        <v>-9.995390289131853</v>
+        <v>-8.917699516312453</v>
       </c>
       <c r="F69">
-        <v>-5.364199457920759</v>
+        <v>-6.544432139886798</v>
       </c>
       <c r="G69">
-        <v>-3.338186434646896</v>
+        <v>-4.540394494505532</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.5576323803404986</v>
       </c>
       <c r="E70">
-        <v>-10.27221137674673</v>
+        <v>-9.72623137953795</v>
       </c>
       <c r="F70">
-        <v>-5.598880127147196</v>
+        <v>-6.507211487535661</v>
       </c>
       <c r="G70">
-        <v>-4.321968010369957</v>
+        <v>-4.703700395412239</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.7343142923754198</v>
       </c>
       <c r="E71">
-        <v>-10.9356056480264</v>
+        <v>-9.337063380266775</v>
       </c>
       <c r="F71">
-        <v>-5.664850188907784</v>
+        <v>-6.605527554839663</v>
       </c>
       <c r="G71">
-        <v>-3.359320957369603</v>
+        <v>-5.664225388721921</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.9674255230788212</v>
       </c>
       <c r="E72">
-        <v>-11.3340615474873</v>
+        <v>-11.16792089309389</v>
       </c>
       <c r="F72">
-        <v>-5.56987930442367</v>
+        <v>-6.701325133811637</v>
       </c>
       <c r="G72">
-        <v>-4.407482712194872</v>
+        <v>-3.98832129928559</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.244577206312475</v>
       </c>
       <c r="E73">
-        <v>-11.0927119967745</v>
+        <v>-9.525869047068575</v>
       </c>
       <c r="F73">
-        <v>-5.982854377463237</v>
+        <v>-6.549205033589453</v>
       </c>
       <c r="G73">
-        <v>-4.137633524197799</v>
+        <v>-5.361585247158367</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.549096696323354</v>
       </c>
       <c r="E74">
-        <v>-10.97790612373204</v>
+        <v>-11.10873826628765</v>
       </c>
       <c r="F74">
-        <v>-5.688893220263028</v>
+        <v>-6.804943052594052</v>
       </c>
       <c r="G74">
-        <v>-3.644421828666099</v>
+        <v>-4.503121062278877</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.865304630938923</v>
       </c>
       <c r="E75">
-        <v>-12.1018009168517</v>
+        <v>-11.02803180252295</v>
       </c>
       <c r="F75">
-        <v>-5.892385177043758</v>
+        <v>-6.6380042161211</v>
       </c>
       <c r="G75">
-        <v>-4.233146073551311</v>
+        <v>-4.639187794488462</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>2.176996173510266</v>
       </c>
       <c r="E76">
-        <v>-12.54610761564027</v>
+        <v>-12.24360555192789</v>
       </c>
       <c r="F76">
-        <v>-6.065778802901562</v>
+        <v>-6.93135723024978</v>
       </c>
       <c r="G76">
-        <v>-3.88525077446592</v>
+        <v>-4.314525903997676</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>2.467036460282102</v>
       </c>
       <c r="E77">
-        <v>-12.47767784491037</v>
+        <v>-13.02958108612118</v>
       </c>
       <c r="F77">
-        <v>-6.193768372016674</v>
+        <v>-6.625773255336162</v>
       </c>
       <c r="G77">
-        <v>-4.258441952016883</v>
+        <v>-5.215686194697146</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>2.723375427893371</v>
       </c>
       <c r="E78">
-        <v>-13.03952561504203</v>
+        <v>-13.48562106106363</v>
       </c>
       <c r="F78">
-        <v>-6.226855156002035</v>
+        <v>-7.145646102109019</v>
       </c>
       <c r="G78">
-        <v>-3.254581917598141</v>
+        <v>-4.453297351912846</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>2.935806093847565</v>
       </c>
       <c r="E79">
-        <v>-14.17481857723899</v>
+        <v>-13.94608535511157</v>
       </c>
       <c r="F79">
-        <v>-6.248606564897638</v>
+        <v>-6.74535017862846</v>
       </c>
       <c r="G79">
-        <v>-3.606413455329726</v>
+        <v>-4.185043846865701</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>3.09699300837072</v>
       </c>
       <c r="E80">
-        <v>-13.45784340150058</v>
+        <v>-13.35244769744606</v>
       </c>
       <c r="F80">
-        <v>-6.602085765958934</v>
+        <v>-7.186252717707365</v>
       </c>
       <c r="G80">
-        <v>-4.024614810032619</v>
+        <v>-4.28230436426395</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>3.205639633874902</v>
       </c>
       <c r="E81">
-        <v>-14.30673302508243</v>
+        <v>-14.06715863618064</v>
       </c>
       <c r="F81">
-        <v>-6.392161191676168</v>
+        <v>-6.970842977986474</v>
       </c>
       <c r="G81">
-        <v>-4.20707883797509</v>
+        <v>-4.081635646401026</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>3.261787896603133</v>
       </c>
       <c r="E82">
-        <v>-15.83412843770754</v>
+        <v>-15.06173832553726</v>
       </c>
       <c r="F82">
-        <v>-6.646046670686181</v>
+        <v>-7.226823699922614</v>
       </c>
       <c r="G82">
-        <v>-3.199656656556093</v>
+        <v>-5.168438088760668</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>3.26838660938891</v>
       </c>
       <c r="E83">
-        <v>-16.90209204835847</v>
+        <v>-15.45851416114133</v>
       </c>
       <c r="F83">
-        <v>-6.518125992778391</v>
+        <v>-7.506413913719646</v>
       </c>
       <c r="G83">
-        <v>-3.879930727784312</v>
+        <v>-4.761585284166396</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>3.233056436126241</v>
       </c>
       <c r="E84">
-        <v>-17.58517612462348</v>
+        <v>-17.01942933837121</v>
       </c>
       <c r="F84">
-        <v>-6.466166185398738</v>
+        <v>-7.373934934260742</v>
       </c>
       <c r="G84">
-        <v>-3.664232133173098</v>
+        <v>-4.817973806336803</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.163890107724245</v>
       </c>
       <c r="E85">
-        <v>-18.67990754513374</v>
+        <v>-17.31546926967465</v>
       </c>
       <c r="F85">
-        <v>-6.68907952374698</v>
+        <v>-7.40346669439242</v>
       </c>
       <c r="G85">
-        <v>-3.661348648008392</v>
+        <v>-4.636228166776354</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.067566188815521</v>
       </c>
       <c r="E86">
-        <v>-19.41294068970336</v>
+        <v>-19.61585708151306</v>
       </c>
       <c r="F86">
-        <v>-6.776606594502051</v>
+        <v>-7.702635868495551</v>
       </c>
       <c r="G86">
-        <v>-3.493503989167343</v>
+        <v>-4.604205259774983</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.950338393811962</v>
       </c>
       <c r="E87">
-        <v>-21.52308730847954</v>
+        <v>-21.39697836431393</v>
       </c>
       <c r="F87">
-        <v>-6.849273752652554</v>
+        <v>-7.602154875205144</v>
       </c>
       <c r="G87">
-        <v>-3.442951958782672</v>
+        <v>-5.085856530283548</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.814485416961304</v>
       </c>
       <c r="E88">
-        <v>-22.88931433117166</v>
+        <v>-21.57977474610756</v>
       </c>
       <c r="F88">
-        <v>-7.048261253883295</v>
+        <v>-7.661751312509045</v>
       </c>
       <c r="G88">
-        <v>-3.61956956330279</v>
+        <v>-4.344721389861369</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.658488261462184</v>
       </c>
       <c r="E89">
-        <v>-24.09924107348904</v>
+        <v>-23.09186844506075</v>
       </c>
       <c r="F89">
-        <v>-6.945165562126497</v>
+        <v>-7.709976741340092</v>
       </c>
       <c r="G89">
-        <v>-3.251221713875781</v>
+        <v>-4.345585442247119</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.480419810258857</v>
       </c>
       <c r="E90">
-        <v>-25.39623225707789</v>
+        <v>-24.6068920666969</v>
       </c>
       <c r="F90">
-        <v>-7.057228196776514</v>
+        <v>-7.720231237142563</v>
       </c>
       <c r="G90">
-        <v>-3.242455389287791</v>
+        <v>-4.124877992234987</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.277195244354402</v>
       </c>
       <c r="E91">
-        <v>-26.7682964827659</v>
+        <v>-26.2052396100742</v>
       </c>
       <c r="F91">
-        <v>-6.925300346976182</v>
+        <v>-7.319577396125114</v>
       </c>
       <c r="G91">
-        <v>-3.75443125693608</v>
+        <v>-3.960621964758507</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.044446214118242</v>
       </c>
       <c r="E92">
-        <v>-28.44314353755477</v>
+        <v>-28.53861735505849</v>
       </c>
       <c r="F92">
-        <v>-7.231901061087513</v>
+        <v>-7.67982456441604</v>
       </c>
       <c r="G92">
-        <v>-3.527599297676297</v>
+        <v>-5.229309089591248</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.778987416855434</v>
       </c>
       <c r="E93">
-        <v>-30.33522149049158</v>
+        <v>-30.63646237419283</v>
       </c>
       <c r="F93">
-        <v>-7.316881532730557</v>
+        <v>-7.561077107096954</v>
       </c>
       <c r="G93">
-        <v>-4.159254697114779</v>
+        <v>-4.536670130773851</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.475653638895582</v>
       </c>
       <c r="E94">
-        <v>-32.33211097433593</v>
+        <v>-32.2248246323832</v>
       </c>
       <c r="F94">
-        <v>-7.1776630927485</v>
+        <v>-7.880101598188428</v>
       </c>
       <c r="G94">
-        <v>-4.134051513924307</v>
+        <v>-3.907189759754671</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.130228465974198</v>
       </c>
       <c r="E95">
-        <v>-35.52344887633944</v>
+        <v>-34.30254058455346</v>
       </c>
       <c r="F95">
-        <v>-6.934280751369681</v>
+        <v>-7.610903266682031</v>
       </c>
       <c r="G95">
-        <v>-4.704392299429947</v>
+        <v>-6.434986601175039</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.7367215765891442</v>
       </c>
       <c r="E96">
-        <v>-37.44789862572008</v>
+        <v>-37.06964198457039</v>
       </c>
       <c r="F96">
-        <v>-7.269849822233273</v>
+        <v>-7.610071425149947</v>
       </c>
       <c r="G96">
-        <v>-5.108758884324226</v>
+        <v>-5.478162797778262</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.2997681591546656</v>
       </c>
       <c r="E97">
-        <v>-39.09282831697728</v>
+        <v>-38.6988216432289</v>
       </c>
       <c r="F97">
-        <v>-7.2916344889531</v>
+        <v>-7.560936553196958</v>
       </c>
       <c r="G97">
-        <v>-5.549495122512939</v>
+        <v>-5.573016548569461</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.1919579063775168</v>
       </c>
       <c r="E98">
-        <v>-41.72159389300789</v>
+        <v>-41.73941117399107</v>
       </c>
       <c r="F98">
-        <v>-6.678852346871551</v>
+        <v>-7.918751941054728</v>
       </c>
       <c r="G98">
-        <v>-6.129045845708831</v>
+        <v>-7.295357660285149</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.7121276593209261</v>
       </c>
       <c r="E99">
-        <v>-43.74676143279314</v>
+        <v>-44.42901453407774</v>
       </c>
       <c r="F99">
-        <v>-6.99275671673841</v>
+        <v>-7.259507430752495</v>
       </c>
       <c r="G99">
-        <v>-6.651641943447102</v>
+        <v>-7.163415867817496</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.282752716703615</v>
       </c>
       <c r="E100">
-        <v>-46.36296049345247</v>
+        <v>-45.05119063493959</v>
       </c>
       <c r="F100">
-        <v>-7.073935898257921</v>
+        <v>-7.652418137622882</v>
       </c>
       <c r="G100">
-        <v>-8.173089220203197</v>
+        <v>-7.547022021635006</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.839435646530948</v>
       </c>
       <c r="E101">
-        <v>-48.66325660369223</v>
+        <v>-47.86282504834795</v>
       </c>
       <c r="F101">
-        <v>-7.207615326800727</v>
+        <v>-7.107067817861871</v>
       </c>
       <c r="G101">
-        <v>-7.581080914143028</v>
+        <v>-8.35913525841916</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.445408622228255</v>
       </c>
       <c r="E102">
-        <v>-51.75331744875119</v>
+        <v>-50.21244529747925</v>
       </c>
       <c r="F102">
-        <v>-6.760590180652733</v>
+        <v>-6.931608247637377</v>
       </c>
       <c r="G102">
-        <v>-8.323844842970528</v>
+        <v>-8.184715856137117</v>
       </c>
     </row>
   </sheetData>
